--- a/スケジュール/スケジュール.xlsx
+++ b/スケジュール/スケジュール.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\新しいフォルダー\就職作品　制作\git_project\スケジュール\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\就職作品\Employment-work\スケジュール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F8108D-C84F-4A2C-A1E0-39C2C040138D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFAF885-F6A7-4E01-ACAD-6BAC50920E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1875" yWindow="-12450" windowWidth="19980" windowHeight="11295" activeTab="2" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
+    <workbookView xWindow="1110" yWindow="2625" windowWidth="16710" windowHeight="11295" activeTab="5" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
   </bookViews>
   <sheets>
     <sheet name="5月" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
   <si>
     <t>5月</t>
     <rPh sb="1" eb="2">
@@ -207,6 +207,37 @@
     <t>eneny</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>ステージ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>重力操作</t>
+    <rPh sb="0" eb="2">
+      <t>ジュウリョク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソウサ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Enemyとギミック</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アイテム配置、アイテム実装、ステージ完成</t>
+    <rPh sb="4" eb="6">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -261,7 +292,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -307,6 +338,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,7 +424,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -473,6 +516,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2277,22 +2338,26 @@
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9"/>
-      <c r="Y3" s="9"/>
-      <c r="Z3" s="9"/>
-      <c r="AA3" s="9"/>
-      <c r="AB3" s="9"/>
-      <c r="AC3" s="9"/>
-      <c r="AD3" s="9"/>
-      <c r="AE3" s="9"/>
+      <c r="P3" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q3" s="31"/>
+      <c r="R3" s="32"/>
+      <c r="S3" s="31"/>
+      <c r="T3" s="31"/>
+      <c r="U3" s="31"/>
+      <c r="V3" s="31"/>
+      <c r="W3" s="31"/>
+      <c r="X3" s="31"/>
+      <c r="Y3" s="31"/>
+      <c r="Z3" s="31"/>
+      <c r="AA3" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB3" s="34"/>
+      <c r="AC3" s="33"/>
+      <c r="AD3" s="33"/>
+      <c r="AE3" s="33"/>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A4" s="7"/>
@@ -2613,37 +2678,39 @@
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9"/>
-      <c r="Y3" s="9"/>
-      <c r="Z3" s="9"/>
-      <c r="AA3" s="9"/>
-      <c r="AB3" s="9"/>
-      <c r="AC3" s="9"/>
-      <c r="AD3" s="9"/>
-      <c r="AE3" s="9"/>
-      <c r="AF3" s="9"/>
+      <c r="B3" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="20"/>
+      <c r="U3" s="20"/>
+      <c r="V3" s="20"/>
+      <c r="W3" s="20"/>
+      <c r="X3" s="20"/>
+      <c r="Y3" s="20"/>
+      <c r="Z3" s="20"/>
+      <c r="AA3" s="20"/>
+      <c r="AB3" s="20"/>
+      <c r="AC3" s="20"/>
+      <c r="AD3" s="20"/>
+      <c r="AE3" s="20"/>
+      <c r="AF3" s="20"/>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A4" s="7"/>
@@ -2966,21 +3033,23 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
+      <c r="B3" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
       <c r="Q3" s="9"/>
       <c r="R3" s="11"/>
       <c r="S3" s="9"/>
@@ -3907,6 +3976,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005F0D9E193D28814892BA96752E68B42F" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="7ef2c4f7c5cf37d6221d7b1dda883374">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c" xmlns:ns3="26553de7-2a3a-444c-a024-df4cb947fd03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="725cefcd41332f88909580cd13155635" ns2:_="" ns3:_="">
     <xsd:import namespace="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
@@ -4101,27 +4190,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
+    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{974AEB67-0EB4-422A-8375-3AEC86DF31AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4138,23 +4226,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
-    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/スケジュール/スケジュール.xlsx
+++ b/スケジュール/スケジュール.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\就職作品\Employment-work\スケジュール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFAF885-F6A7-4E01-ACAD-6BAC50920E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE299B4F-42DE-4472-B35A-BBC14CB727DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1110" yWindow="2625" windowWidth="16710" windowHeight="11295" activeTab="5" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
+    <workbookView xWindow="6285" yWindow="1845" windowWidth="16710" windowHeight="11295" activeTab="8" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
   </bookViews>
   <sheets>
     <sheet name="5月" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
   <si>
     <t>5月</t>
     <rPh sb="1" eb="2">
@@ -238,6 +238,24 @@
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>ボスエネミー追加</t>
+    <rPh sb="6" eb="8">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ブラッシュアップ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>調整</t>
+    <rPh sb="0" eb="2">
+      <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -424,7 +442,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -534,6 +552,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3050,21 +3071,23 @@
       <c r="N3" s="20"/>
       <c r="O3" s="20"/>
       <c r="P3" s="20"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9"/>
-      <c r="Y3" s="9"/>
-      <c r="Z3" s="9"/>
-      <c r="AA3" s="9"/>
-      <c r="AB3" s="9"/>
-      <c r="AC3" s="9"/>
-      <c r="AD3" s="9"/>
-      <c r="AE3" s="9"/>
+      <c r="Q3" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="32"/>
+      <c r="S3" s="31"/>
+      <c r="T3" s="31"/>
+      <c r="U3" s="31"/>
+      <c r="V3" s="31"/>
+      <c r="W3" s="31"/>
+      <c r="X3" s="31"/>
+      <c r="Y3" s="31"/>
+      <c r="Z3" s="31"/>
+      <c r="AA3" s="31"/>
+      <c r="AB3" s="31"/>
+      <c r="AC3" s="31"/>
+      <c r="AD3" s="31"/>
+      <c r="AE3" s="31"/>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A4" s="7"/>
@@ -3381,36 +3404,38 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9"/>
-      <c r="Y3" s="9"/>
-      <c r="Z3" s="9"/>
-      <c r="AA3" s="9"/>
-      <c r="AB3" s="9"/>
-      <c r="AC3" s="9"/>
-      <c r="AD3" s="9"/>
-      <c r="AE3" s="9"/>
+      <c r="B3" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="37"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
+      <c r="V3" s="27"/>
+      <c r="W3" s="27"/>
+      <c r="X3" s="27"/>
+      <c r="Y3" s="27"/>
+      <c r="Z3" s="27"/>
+      <c r="AA3" s="27"/>
+      <c r="AB3" s="27"/>
+      <c r="AC3" s="27"/>
+      <c r="AD3" s="27"/>
+      <c r="AE3" s="27"/>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.4">
       <c r="A4" s="7"/>
@@ -3730,24 +3755,28 @@
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.4">
       <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="9"/>
+      <c r="B3" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
+      <c r="Q3" s="31"/>
+      <c r="R3" s="32"/>
+      <c r="S3" s="31"/>
       <c r="T3" s="9"/>
       <c r="U3" s="9"/>
       <c r="V3" s="9"/>
@@ -3976,26 +4005,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005F0D9E193D28814892BA96752E68B42F" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="7ef2c4f7c5cf37d6221d7b1dda883374">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c" xmlns:ns3="26553de7-2a3a-444c-a024-df4cb947fd03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="725cefcd41332f88909580cd13155635" ns2:_="" ns3:_="">
     <xsd:import namespace="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
@@ -4190,10 +4199,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{974AEB67-0EB4-422A-8375-3AEC86DF31AC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
+    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4210,20 +4250,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{974AEB67-0EB4-422A-8375-3AEC86DF31AC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
-    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>